--- a/trade_log.xlsx
+++ b/trade_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NVDL</t>
+          <t>JNUG</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1142,29 +1142,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-08-04 09:50</t>
+          <t>2025-08-06 09:45</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>86.53</v>
+        <v>163.75</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-08-04 11:55</t>
+          <t>2025-08-06 9:50</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>88.26000000000001</v>
+        <v>163.75</v>
       </c>
       <c r="H18" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Entry 86.53, Target 88.26, Stop 85.66</t>
+          <t>I think I crossed the entry with another ticker just closed this at no p or l</t>
         </is>
       </c>
     </row>
@@ -1184,29 +1184,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-08-06 09:45</t>
+          <t>2025-08-07 09:49</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>163.75</v>
+        <v>89.92</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-08-06 9:50</t>
+          <t>2025-08-07 10:05</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>163.75</v>
+        <v>89.02</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>I think I crossed the entry with another ticker just closed this at no p or l</t>
+          <t>Stopped out, Entry 89.92, Target 91.72, Stop 89.02</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JNUG</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1226,29 +1226,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-08-07 09:49</t>
+          <t>2025-08-11 09:15</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>89.92</v>
+        <v>171.35</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-08-07 10:05</t>
+          <t>2025-08-11 10:05</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>89.02</v>
+        <v>174.78</v>
       </c>
       <c r="H20" t="n">
-        <v>-90</v>
+        <v>343</v>
       </c>
       <c r="I20" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Stopped out, Entry 89.92, Target 91.72, Stop 89.02</t>
+          <t>Entry 171.35, Target 174.78, Stop 169.64</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ETHU</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1268,29 +1268,29 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-08-11 09:15</t>
+          <t>2025-08-12 11:28</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>171.35</v>
+        <v>162.78</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-08-11 10:05</t>
+          <t>2025-08-12 12:00</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>174.78</v>
+        <v>166.04</v>
       </c>
       <c r="H21" t="n">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="I21" t="n">
         <v>2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Entry 171.35, Target 174.78, Stop 169.64</t>
+          <t>Entry 162.78, Target 166.04, Stop 161.15</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ETHU</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1310,29 +1310,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-08-12 11:28</t>
+          <t>2025-08-18 09:55</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>162.78</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-08-12 12:00</t>
+          <t>2025-08-18 11:05</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>166.04</v>
+        <v>71.77</v>
       </c>
       <c r="H22" t="n">
-        <v>326</v>
+        <v>-72</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>-0.99</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Entry 162.78, Target 166.04, Stop 161.15</t>
+          <t>LABU Entry 72.49, Target 73.94, Stop 71.77</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,743 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-08-18 09:55</t>
+          <t>2025-08-26 10:41</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>72.48999999999999</v>
+        <v>161.26</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-08-18 11:05</t>
+          <t>2025-08-26 15:45</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>71.77</v>
+        <v>164.5</v>
       </c>
       <c r="H23" t="n">
-        <v>-72</v>
+        <v>324</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.99</v>
+        <v>2.01</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>LABU Entry 72.49, Target 73.94, Stop 71.77</t>
+          <t>trading ETHU but not available in the drop down Entry 161.26, Target 164.48, Stop 159.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NVDL</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>100</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-08-28 10:17</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2025-08-28 10.25</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>86.70999999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-89</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>87.59, Target 89.34, Stop 86.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GDXU</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>100</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-09-05 10:02</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>135.01</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2025-09-05 11:10</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>137.71</v>
+      </c>
+      <c r="H25" t="n">
+        <v>270</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Without stop this trade was profitable going to work without stop a while see what happensEntry 135.01, Target 137.71, Stop 133.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NVDL</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>100</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-09-11 09:50</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>86.47</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2025-09-11 15:45</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>85.20999999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-126</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Entry 86.47, Target 88.20, Stop 85.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TSLT</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>100</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-09-16 10:12</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2025-09-16 11:10</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="H27" t="n">
+        <v>51</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Entry 25.46, Target 25.97, Stop 25.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SMCX</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>100</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-09-29 09:45</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2025-09-29 9:50</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>37</v>
+      </c>
+      <c r="H28" t="n">
+        <v>70</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Entry 36.21, Target 36.93, Stop 35.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LABU</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>100</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-10-03 10:02</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102.08</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2025-10-03 10:35</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>104.12</v>
+      </c>
+      <c r="H29" t="n">
+        <v>204</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Entry 102.08, Target 104.12, Stop 101.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SMCX</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>100</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-10-06 10:12</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2025-10-06 10:25</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>51.19</v>
+      </c>
+      <c r="H30" t="n">
+        <v>100</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Entry 50.19, Target 51.19, Stop 49.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SMCX</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>100</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-10-14 10:41</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2025-10-14 10:50</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-58</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Entry 49.39, Target 50.38, Stop 48.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DFEN</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>100</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-10-15 10:25</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2025-10-15 11:45</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-76</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Entry 71.10, Target 72.52, Stop 70.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MSTX</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>100</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-10-17 10:15</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2025-10-17 10:20</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixing mistaken entry </t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MSTX</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>100</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-10-17 10:15</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2025-10-17 10:20</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>16.31, Target 16.64, Stop 16.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ETHU</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>100</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-10-20 10:36</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>117.44</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2025-10-20 11:55</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-114</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Entry 117.47, Target 119.82, Stop 116.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MSFU</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>100</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-10-28 09:59</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2025-10-28 10:30</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>56.97</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-58</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Entry $$57.55	$58.70	$56.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NVDL</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>100</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>117.65</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2025-10-29 116.47</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>116.47</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-118</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Entry $117.65, Target $120.00, Stop $116.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NUGT</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>100</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-10-30 09:45</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>130.08</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2025-10-30 10.05</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>132.68</v>
+      </c>
+      <c r="H38" t="n">
+        <v>260</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Entry $130.08, Target $132.68, Stop $128.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MSTX</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>100</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-10-17 10:15</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2025-10-17 10:20</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fixing mistaken entry </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>100</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-10-31 12:30</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>256.31</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2025-10-31 15:45</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>257.29</v>
+      </c>
+      <c r="H40" t="n">
+        <v>98</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Closed at end of day $256.37, Target $261.49, Stop $253.80</t>
         </is>
       </c>
     </row>
